--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
@@ -63,12 +63,12 @@
     <t xml:space="preserve">Puerto Octay</t>
   </si>
   <si>
+    <t xml:space="preserve">Futaleufú</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ancud</t>
   </si>
   <si>
-    <t xml:space="preserve">Futaleufú</t>
-  </si>
-  <si>
     <t xml:space="preserve">Frutillar</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:29</t>
+    <t xml:space="preserve">2026-09-09 23:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -718,7 +718,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>10202</v>
+        <v>10402</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
@@ -735,7 +735,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>10402</v>
+        <v>10202</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:26</t>
+    <t xml:space="preserve">2026-09-17 14:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
@@ -63,12 +63,12 @@
     <t xml:space="preserve">Puerto Octay</t>
   </si>
   <si>
+    <t xml:space="preserve">Ancud</t>
+  </si>
+  <si>
     <t xml:space="preserve">Futaleufú</t>
   </si>
   <si>
-    <t xml:space="preserve">Ancud</t>
-  </si>
-  <si>
     <t xml:space="preserve">Frutillar</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:21</t>
+    <t xml:space="preserve">2026-09-23 12:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -718,7 +718,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>10402</v>
+        <v>10202</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
@@ -735,7 +735,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>10202</v>
+        <v>10402</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:49</t>
+    <t xml:space="preserve">2026-10-01 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -166,9 +166,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1141,7 @@
         <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:11</t>
+    <t xml:space="preserve">2026-10-02 11:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:22</t>
+    <t xml:space="preserve">2026-10-02 15:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2023_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:09</t>
+    <t xml:space="preserve">2026-10-05 12:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
